--- a/artfynd/A 56187-2019 artfynd.xlsx
+++ b/artfynd/A 56187-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120467463</v>
+        <v>120467500</v>
       </c>
       <c r="B2" t="n">
         <v>57320</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518865</v>
+        <v>518669</v>
       </c>
       <c r="R2" t="n">
-        <v>7034523</v>
+        <v>7034370</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120467501</v>
+        <v>120467483</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518669</v>
+        <v>518888</v>
       </c>
       <c r="R3" t="n">
-        <v>7034375</v>
+        <v>7034422</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120467492</v>
+        <v>120467452</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518765</v>
+        <v>518591</v>
       </c>
       <c r="R4" t="n">
-        <v>7034291</v>
+        <v>7034299</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120467467</v>
+        <v>120467514</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518818</v>
+        <v>518706</v>
       </c>
       <c r="R5" t="n">
-        <v>7034622</v>
+        <v>7034110</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120467614</v>
+        <v>120467470</v>
       </c>
       <c r="B6" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519001</v>
+        <v>518931</v>
       </c>
       <c r="R6" t="n">
-        <v>7034557</v>
+        <v>7034579</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1179,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120467451</v>
+        <v>120467463</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518599</v>
+        <v>518865</v>
       </c>
       <c r="R7" t="n">
-        <v>7034304</v>
+        <v>7034523</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120467502</v>
+        <v>120467516</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1352,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518668</v>
+        <v>518672</v>
       </c>
       <c r="R8" t="n">
-        <v>7034378</v>
+        <v>7034063</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120467505</v>
+        <v>120467475</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1459,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518654</v>
+        <v>519003</v>
       </c>
       <c r="R9" t="n">
-        <v>7034382</v>
+        <v>7034509</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120467469</v>
+        <v>120467520</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1566,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518862</v>
+        <v>518661</v>
       </c>
       <c r="R10" t="n">
-        <v>7034625</v>
+        <v>7034107</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120467472</v>
+        <v>120467492</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1673,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518975</v>
+        <v>518765</v>
       </c>
       <c r="R11" t="n">
-        <v>7034569</v>
+        <v>7034291</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1718,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120467500</v>
+        <v>120467455</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1780,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518669</v>
+        <v>518581</v>
       </c>
       <c r="R12" t="n">
-        <v>7034370</v>
+        <v>7034337</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1825,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120467460</v>
+        <v>120467498</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1887,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518817</v>
+        <v>518670</v>
       </c>
       <c r="R13" t="n">
-        <v>7034450</v>
+        <v>7034369</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1954,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120467606</v>
+        <v>120467488</v>
       </c>
       <c r="B14" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1970,16 +1975,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1994,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518821</v>
+        <v>518792</v>
       </c>
       <c r="R14" t="n">
-        <v>7034294</v>
+        <v>7034416</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +2039,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,7 +2066,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120467480</v>
+        <v>120467489</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2101,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518869</v>
+        <v>518800</v>
       </c>
       <c r="R15" t="n">
-        <v>7034440</v>
+        <v>7034389</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2168,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120467452</v>
+        <v>120467617</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2184,21 +2189,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518591</v>
+        <v>518787</v>
       </c>
       <c r="R16" t="n">
-        <v>7034299</v>
+        <v>7034394</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2244,11 +2249,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,7 +2275,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120467462</v>
+        <v>120467471</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518816</v>
+        <v>518950</v>
       </c>
       <c r="R17" t="n">
-        <v>7034466</v>
+        <v>7034577</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2382,10 +2382,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120467618</v>
+        <v>120467504</v>
       </c>
       <c r="B18" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2398,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518820</v>
+        <v>518664</v>
       </c>
       <c r="R18" t="n">
-        <v>7034294</v>
+        <v>7034392</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2458,6 +2458,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,7 +2489,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120467474</v>
+        <v>120467466</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2524,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519042</v>
+        <v>518836</v>
       </c>
       <c r="R19" t="n">
-        <v>7034514</v>
+        <v>7034593</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2591,7 +2596,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120467464</v>
+        <v>120467495</v>
       </c>
       <c r="B20" t="n">
         <v>57320</v>
@@ -2631,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518883</v>
+        <v>518708</v>
       </c>
       <c r="R20" t="n">
-        <v>7034525</v>
+        <v>7034368</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2676,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,7 +2703,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120467479</v>
+        <v>120467502</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2738,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518926</v>
+        <v>518668</v>
       </c>
       <c r="R21" t="n">
-        <v>7034518</v>
+        <v>7034378</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,7 +2810,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120467487</v>
+        <v>120467457</v>
       </c>
       <c r="B22" t="n">
         <v>57320</v>
@@ -2845,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518821</v>
+        <v>518595</v>
       </c>
       <c r="R22" t="n">
-        <v>7034432</v>
+        <v>7034382</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2890,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack äldre 2 granar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,10 +2917,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120467617</v>
+        <v>120467485</v>
       </c>
       <c r="B23" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2928,21 +2933,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2952,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518787</v>
+        <v>518905</v>
       </c>
       <c r="R23" t="n">
-        <v>7034394</v>
+        <v>7034396</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2988,6 +2993,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,7 +3024,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120467515</v>
+        <v>120467505</v>
       </c>
       <c r="B24" t="n">
         <v>57320</v>
@@ -3054,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518690</v>
+        <v>518654</v>
       </c>
       <c r="R24" t="n">
-        <v>7034072</v>
+        <v>7034382</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3121,10 +3131,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120467510</v>
+        <v>120467606</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3137,16 +3147,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3161,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518659</v>
+        <v>518821</v>
       </c>
       <c r="R25" t="n">
-        <v>7034117</v>
+        <v>7034294</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3201,7 +3211,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,7 +3238,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120467490</v>
+        <v>120467494</v>
       </c>
       <c r="B26" t="n">
         <v>57320</v>
@@ -3268,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518794</v>
+        <v>518723</v>
       </c>
       <c r="R26" t="n">
-        <v>7034387</v>
+        <v>7034370</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3335,7 +3345,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120467458</v>
+        <v>120467490</v>
       </c>
       <c r="B27" t="n">
         <v>57320</v>
@@ -3375,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518758</v>
+        <v>518794</v>
       </c>
       <c r="R27" t="n">
-        <v>7034403</v>
+        <v>7034387</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3442,7 +3452,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120467457</v>
+        <v>120467497</v>
       </c>
       <c r="B28" t="n">
         <v>57320</v>
@@ -3482,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518595</v>
+        <v>518674</v>
       </c>
       <c r="R28" t="n">
-        <v>7034382</v>
+        <v>7034370</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3522,7 +3532,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre 2 granar</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3549,7 +3559,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120467478</v>
+        <v>120467460</v>
       </c>
       <c r="B29" t="n">
         <v>57320</v>
@@ -3589,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518932</v>
+        <v>518817</v>
       </c>
       <c r="R29" t="n">
-        <v>7034518</v>
+        <v>7034450</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3629,7 +3639,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3656,10 +3666,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120467465</v>
+        <v>120467618</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3672,21 +3682,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3696,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518877</v>
+        <v>518820</v>
       </c>
       <c r="R30" t="n">
-        <v>7034539</v>
+        <v>7034294</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3732,11 +3742,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Bohål ca 3,5-4 m upp i gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3763,7 +3768,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120467459</v>
+        <v>120467513</v>
       </c>
       <c r="B31" t="n">
         <v>57320</v>
@@ -3803,10 +3808,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>518766</v>
+        <v>518705</v>
       </c>
       <c r="R31" t="n">
-        <v>7034415</v>
+        <v>7034105</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3870,7 +3875,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120467475</v>
+        <v>120467478</v>
       </c>
       <c r="B32" t="n">
         <v>57320</v>
@@ -3910,10 +3915,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519003</v>
+        <v>518932</v>
       </c>
       <c r="R32" t="n">
-        <v>7034509</v>
+        <v>7034518</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,7 +3955,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3977,7 +3982,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120467483</v>
+        <v>120467467</v>
       </c>
       <c r="B33" t="n">
         <v>57320</v>
@@ -4017,10 +4022,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518888</v>
+        <v>518818</v>
       </c>
       <c r="R33" t="n">
-        <v>7034422</v>
+        <v>7034622</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4084,7 +4089,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120467508</v>
+        <v>120467453</v>
       </c>
       <c r="B34" t="n">
         <v>57320</v>
@@ -4124,10 +4129,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518608</v>
+        <v>518578</v>
       </c>
       <c r="R34" t="n">
-        <v>7034344</v>
+        <v>7034314</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4298,7 +4303,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120467484</v>
+        <v>120467454</v>
       </c>
       <c r="B36" t="n">
         <v>57320</v>
@@ -4338,10 +4343,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518914</v>
+        <v>518574</v>
       </c>
       <c r="R36" t="n">
-        <v>7034381</v>
+        <v>7034340</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4405,7 +4410,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120467456</v>
+        <v>120467469</v>
       </c>
       <c r="B37" t="n">
         <v>57320</v>
@@ -4445,10 +4450,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518584</v>
+        <v>518862</v>
       </c>
       <c r="R37" t="n">
-        <v>7034352</v>
+        <v>7034625</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4512,7 +4517,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120467514</v>
+        <v>120467462</v>
       </c>
       <c r="B38" t="n">
         <v>57320</v>
@@ -4552,10 +4557,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>518706</v>
+        <v>518816</v>
       </c>
       <c r="R38" t="n">
-        <v>7034110</v>
+        <v>7034466</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4592,7 +4597,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4619,7 +4624,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120467466</v>
+        <v>120467459</v>
       </c>
       <c r="B39" t="n">
         <v>57320</v>
@@ -4659,10 +4664,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>518836</v>
+        <v>518766</v>
       </c>
       <c r="R39" t="n">
-        <v>7034593</v>
+        <v>7034415</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4726,7 +4731,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120467511</v>
+        <v>120467518</v>
       </c>
       <c r="B40" t="n">
         <v>57320</v>
@@ -4766,10 +4771,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>518672</v>
+        <v>518675</v>
       </c>
       <c r="R40" t="n">
-        <v>7034111</v>
+        <v>7034072</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4806,7 +4811,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4833,10 +4838,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120467620</v>
+        <v>120467476</v>
       </c>
       <c r="B41" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4849,21 +4854,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4873,10 +4878,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518727</v>
+        <v>518963</v>
       </c>
       <c r="R41" t="n">
-        <v>7034329</v>
+        <v>7034492</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4909,6 +4914,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4935,10 +4945,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120467489</v>
+        <v>120467611</v>
       </c>
       <c r="B42" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4951,21 +4961,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4975,10 +4985,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518800</v>
+        <v>518883</v>
       </c>
       <c r="R42" t="n">
-        <v>7034389</v>
+        <v>7034541</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5011,11 +5021,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5042,7 +5047,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120467473</v>
+        <v>120467474</v>
       </c>
       <c r="B43" t="n">
         <v>57320</v>
@@ -5082,10 +5087,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519024</v>
+        <v>519042</v>
       </c>
       <c r="R43" t="n">
-        <v>7034532</v>
+        <v>7034514</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5149,10 +5154,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120467613</v>
+        <v>120467510</v>
       </c>
       <c r="B44" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5165,21 +5170,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5189,10 +5194,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518801</v>
+        <v>518659</v>
       </c>
       <c r="R44" t="n">
-        <v>7034574</v>
+        <v>7034117</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5225,6 +5230,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5251,7 +5261,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120467485</v>
+        <v>120467512</v>
       </c>
       <c r="B45" t="n">
         <v>57320</v>
@@ -5291,10 +5301,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518905</v>
+        <v>518685</v>
       </c>
       <c r="R45" t="n">
-        <v>7034396</v>
+        <v>7034116</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5331,7 +5341,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5358,7 +5368,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120467498</v>
+        <v>120467501</v>
       </c>
       <c r="B46" t="n">
         <v>57320</v>
@@ -5398,10 +5408,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518670</v>
+        <v>518669</v>
       </c>
       <c r="R46" t="n">
-        <v>7034369</v>
+        <v>7034375</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5465,7 +5475,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120467519</v>
+        <v>120467491</v>
       </c>
       <c r="B47" t="n">
         <v>57320</v>
@@ -5505,10 +5515,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518664</v>
+        <v>518772</v>
       </c>
       <c r="R47" t="n">
-        <v>7034102</v>
+        <v>7034366</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5572,7 +5582,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120467504</v>
+        <v>120467464</v>
       </c>
       <c r="B48" t="n">
         <v>57320</v>
@@ -5612,10 +5622,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518664</v>
+        <v>518883</v>
       </c>
       <c r="R48" t="n">
-        <v>7034392</v>
+        <v>7034525</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5652,7 +5662,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5679,7 +5689,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120467513</v>
+        <v>120467493</v>
       </c>
       <c r="B49" t="n">
         <v>57320</v>
@@ -5719,10 +5729,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518705</v>
+        <v>518712</v>
       </c>
       <c r="R49" t="n">
-        <v>7034105</v>
+        <v>7034336</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5759,7 +5769,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5786,7 +5796,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120467471</v>
+        <v>120467482</v>
       </c>
       <c r="B50" t="n">
         <v>57320</v>
@@ -5826,10 +5836,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518950</v>
+        <v>518881</v>
       </c>
       <c r="R50" t="n">
-        <v>7034577</v>
+        <v>7034419</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5893,10 +5903,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120467612</v>
+        <v>120467458</v>
       </c>
       <c r="B51" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5909,21 +5919,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5933,10 +5943,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518848</v>
+        <v>518758</v>
       </c>
       <c r="R51" t="n">
-        <v>7034595</v>
+        <v>7034403</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5969,6 +5979,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5995,10 +6010,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120467481</v>
+        <v>120467615</v>
       </c>
       <c r="B52" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6011,21 +6026,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6035,10 +6050,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>518873</v>
+        <v>518904</v>
       </c>
       <c r="R52" t="n">
-        <v>7034419</v>
+        <v>7034422</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6071,11 +6086,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6102,7 +6112,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120467482</v>
+        <v>120467487</v>
       </c>
       <c r="B53" t="n">
         <v>57320</v>
@@ -6142,10 +6152,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518881</v>
+        <v>518821</v>
       </c>
       <c r="R53" t="n">
-        <v>7034419</v>
+        <v>7034432</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6209,10 +6219,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120467454</v>
+        <v>120467620</v>
       </c>
       <c r="B54" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6225,21 +6235,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6249,10 +6259,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>518574</v>
+        <v>518727</v>
       </c>
       <c r="R54" t="n">
-        <v>7034340</v>
+        <v>7034329</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6285,11 +6295,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6316,10 +6321,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120467470</v>
+        <v>120467614</v>
       </c>
       <c r="B55" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6332,21 +6337,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6356,10 +6361,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>518931</v>
+        <v>519001</v>
       </c>
       <c r="R55" t="n">
-        <v>7034579</v>
+        <v>7034557</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6392,11 +6397,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6423,10 +6423,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120467615</v>
+        <v>120467515</v>
       </c>
       <c r="B56" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6439,21 +6439,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6463,10 +6463,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>518904</v>
+        <v>518690</v>
       </c>
       <c r="R56" t="n">
-        <v>7034422</v>
+        <v>7034072</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6499,6 +6499,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6525,7 +6530,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120467453</v>
+        <v>120467509</v>
       </c>
       <c r="B57" t="n">
         <v>57320</v>
@@ -6565,10 +6570,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>518578</v>
+        <v>518608</v>
       </c>
       <c r="R57" t="n">
-        <v>7034314</v>
+        <v>7034284</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6632,10 +6637,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120467450</v>
+        <v>120467612</v>
       </c>
       <c r="B58" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6648,21 +6653,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6672,10 +6677,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>518565</v>
+        <v>518848</v>
       </c>
       <c r="R58" t="n">
-        <v>7034294</v>
+        <v>7034595</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6708,11 +6713,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6739,7 +6739,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120467491</v>
+        <v>120467468</v>
       </c>
       <c r="B59" t="n">
         <v>57320</v>
@@ -6779,10 +6779,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>518772</v>
+        <v>518830</v>
       </c>
       <c r="R59" t="n">
-        <v>7034366</v>
+        <v>7034634</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6846,7 +6846,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120467488</v>
+        <v>120467456</v>
       </c>
       <c r="B60" t="n">
         <v>57320</v>
@@ -6886,10 +6886,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>518792</v>
+        <v>518584</v>
       </c>
       <c r="R60" t="n">
-        <v>7034416</v>
+        <v>7034352</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6953,7 +6953,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120467494</v>
+        <v>120467519</v>
       </c>
       <c r="B61" t="n">
         <v>57320</v>
@@ -6993,10 +6993,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>518723</v>
+        <v>518664</v>
       </c>
       <c r="R61" t="n">
-        <v>7034370</v>
+        <v>7034102</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7060,7 +7060,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120467520</v>
+        <v>120467480</v>
       </c>
       <c r="B62" t="n">
         <v>57320</v>
@@ -7100,10 +7100,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518661</v>
+        <v>518869</v>
       </c>
       <c r="R62" t="n">
-        <v>7034107</v>
+        <v>7034440</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7167,10 +7167,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120467619</v>
+        <v>120467511</v>
       </c>
       <c r="B63" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7183,21 +7183,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7207,10 +7207,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518812</v>
+        <v>518672</v>
       </c>
       <c r="R63" t="n">
-        <v>7034301</v>
+        <v>7034111</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7243,6 +7243,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7269,7 +7274,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120467509</v>
+        <v>120467506</v>
       </c>
       <c r="B64" t="n">
         <v>57320</v>
@@ -7309,10 +7314,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>518608</v>
+        <v>518600</v>
       </c>
       <c r="R64" t="n">
-        <v>7034284</v>
+        <v>7034354</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7478,7 +7483,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120467476</v>
+        <v>120467472</v>
       </c>
       <c r="B66" t="n">
         <v>57320</v>
@@ -7518,10 +7523,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518963</v>
+        <v>518975</v>
       </c>
       <c r="R66" t="n">
-        <v>7034492</v>
+        <v>7034569</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7558,7 +7563,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7585,10 +7590,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120467611</v>
+        <v>120467465</v>
       </c>
       <c r="B67" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7601,21 +7606,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7625,10 +7630,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>518883</v>
+        <v>518877</v>
       </c>
       <c r="R67" t="n">
-        <v>7034541</v>
+        <v>7034539</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7661,6 +7666,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Bohål ca 3,5-4 m upp i gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7687,7 +7697,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120467517</v>
+        <v>120467450</v>
       </c>
       <c r="B68" t="n">
         <v>57320</v>
@@ -7727,10 +7737,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518677</v>
+        <v>518565</v>
       </c>
       <c r="R68" t="n">
-        <v>7034070</v>
+        <v>7034294</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7794,7 +7804,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120467507</v>
+        <v>120467479</v>
       </c>
       <c r="B69" t="n">
         <v>57320</v>
@@ -7834,10 +7844,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>518607</v>
+        <v>518926</v>
       </c>
       <c r="R69" t="n">
-        <v>7034347</v>
+        <v>7034518</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7874,7 +7884,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7901,7 +7911,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120467468</v>
+        <v>120467517</v>
       </c>
       <c r="B70" t="n">
         <v>57320</v>
@@ -7941,10 +7951,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>518830</v>
+        <v>518677</v>
       </c>
       <c r="R70" t="n">
-        <v>7034634</v>
+        <v>7034070</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8008,10 +8018,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120467506</v>
+        <v>120467613</v>
       </c>
       <c r="B71" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8024,21 +8034,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8048,10 +8058,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>518600</v>
+        <v>518801</v>
       </c>
       <c r="R71" t="n">
-        <v>7034354</v>
+        <v>7034574</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8084,11 +8094,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8115,7 +8120,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120467493</v>
+        <v>120467484</v>
       </c>
       <c r="B72" t="n">
         <v>57320</v>
@@ -8155,10 +8160,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>518712</v>
+        <v>518914</v>
       </c>
       <c r="R72" t="n">
-        <v>7034336</v>
+        <v>7034381</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8195,7 +8200,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8222,7 +8227,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120467495</v>
+        <v>120467473</v>
       </c>
       <c r="B73" t="n">
         <v>57320</v>
@@ -8262,10 +8267,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>518708</v>
+        <v>519024</v>
       </c>
       <c r="R73" t="n">
-        <v>7034368</v>
+        <v>7034532</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8329,10 +8334,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120467497</v>
+        <v>120467621</v>
       </c>
       <c r="B74" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8345,21 +8350,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8369,10 +8374,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>518674</v>
+        <v>518701</v>
       </c>
       <c r="R74" t="n">
-        <v>7034370</v>
+        <v>7034127</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8405,11 +8410,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8436,7 +8436,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120467518</v>
+        <v>120467486</v>
       </c>
       <c r="B75" t="n">
         <v>57320</v>
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>518675</v>
+        <v>518842</v>
       </c>
       <c r="R75" t="n">
-        <v>7034072</v>
+        <v>7034430</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8543,7 +8543,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120467455</v>
+        <v>120467508</v>
       </c>
       <c r="B76" t="n">
         <v>57320</v>
@@ -8583,10 +8583,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>518581</v>
+        <v>518608</v>
       </c>
       <c r="R76" t="n">
-        <v>7034337</v>
+        <v>7034344</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8650,7 +8650,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120467486</v>
+        <v>120467507</v>
       </c>
       <c r="B77" t="n">
         <v>57320</v>
@@ -8690,10 +8690,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>518842</v>
+        <v>518607</v>
       </c>
       <c r="R77" t="n">
-        <v>7034430</v>
+        <v>7034347</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8757,7 +8757,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120467512</v>
+        <v>120467481</v>
       </c>
       <c r="B78" t="n">
         <v>57320</v>
@@ -8797,10 +8797,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>518685</v>
+        <v>518873</v>
       </c>
       <c r="R78" t="n">
-        <v>7034116</v>
+        <v>7034419</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8864,10 +8864,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120467516</v>
+        <v>120467619</v>
       </c>
       <c r="B79" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8880,21 +8880,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>518672</v>
+        <v>518812</v>
       </c>
       <c r="R79" t="n">
-        <v>7034063</v>
+        <v>7034301</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8940,11 +8940,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8971,10 +8966,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120467621</v>
+        <v>120467451</v>
       </c>
       <c r="B80" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8987,21 +8982,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9011,10 +9006,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>518701</v>
+        <v>518599</v>
       </c>
       <c r="R80" t="n">
-        <v>7034127</v>
+        <v>7034304</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9047,6 +9042,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">

--- a/artfynd/A 56187-2019 artfynd.xlsx
+++ b/artfynd/A 56187-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120467500</v>
+        <v>120467478</v>
       </c>
       <c r="B2" t="n">
         <v>57320</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518669</v>
+        <v>518932</v>
       </c>
       <c r="R2" t="n">
-        <v>7034370</v>
+        <v>7034518</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120467483</v>
+        <v>120467453</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518888</v>
+        <v>518578</v>
       </c>
       <c r="R3" t="n">
-        <v>7034422</v>
+        <v>7034314</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120467452</v>
+        <v>120467506</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518591</v>
+        <v>518600</v>
       </c>
       <c r="R4" t="n">
-        <v>7034299</v>
+        <v>7034354</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120467514</v>
+        <v>120467485</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518706</v>
+        <v>518905</v>
       </c>
       <c r="R5" t="n">
-        <v>7034110</v>
+        <v>7034396</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120467470</v>
+        <v>120467455</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518931</v>
+        <v>518581</v>
       </c>
       <c r="R6" t="n">
-        <v>7034579</v>
+        <v>7034337</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120467463</v>
+        <v>120467513</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518865</v>
+        <v>518705</v>
       </c>
       <c r="R7" t="n">
-        <v>7034523</v>
+        <v>7034105</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120467516</v>
+        <v>120467459</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518672</v>
+        <v>518766</v>
       </c>
       <c r="R8" t="n">
-        <v>7034063</v>
+        <v>7034415</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120467475</v>
+        <v>120467514</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519003</v>
+        <v>518706</v>
       </c>
       <c r="R9" t="n">
-        <v>7034509</v>
+        <v>7034110</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120467520</v>
+        <v>120467619</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,21 +1547,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518661</v>
+        <v>518812</v>
       </c>
       <c r="R10" t="n">
-        <v>7034107</v>
+        <v>7034301</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,11 +1607,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120467492</v>
+        <v>120467511</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1678,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518765</v>
+        <v>518672</v>
       </c>
       <c r="R11" t="n">
-        <v>7034291</v>
+        <v>7034111</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1713,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120467455</v>
+        <v>120467516</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1785,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518581</v>
+        <v>518672</v>
       </c>
       <c r="R12" t="n">
-        <v>7034337</v>
+        <v>7034063</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1820,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,7 +1847,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120467498</v>
+        <v>120467465</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1892,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518670</v>
+        <v>518877</v>
       </c>
       <c r="R13" t="n">
-        <v>7034369</v>
+        <v>7034539</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1927,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Bohål ca 3,5-4 m upp i gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,7 +1954,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120467488</v>
+        <v>120467489</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -1999,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518792</v>
+        <v>518800</v>
       </c>
       <c r="R14" t="n">
-        <v>7034416</v>
+        <v>7034389</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2066,7 +2061,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120467489</v>
+        <v>120467498</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2106,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518800</v>
+        <v>518670</v>
       </c>
       <c r="R15" t="n">
-        <v>7034389</v>
+        <v>7034369</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2141,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120467617</v>
+        <v>120467606</v>
       </c>
       <c r="B16" t="n">
-        <v>90598</v>
+        <v>57336</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2189,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2213,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518787</v>
+        <v>518821</v>
       </c>
       <c r="R16" t="n">
-        <v>7034394</v>
+        <v>7034294</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2249,6 +2244,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120467471</v>
+        <v>120467615</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518950</v>
+        <v>518904</v>
       </c>
       <c r="R17" t="n">
-        <v>7034577</v>
+        <v>7034422</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2351,11 +2351,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2382,7 +2377,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120467504</v>
+        <v>120467501</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2422,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518664</v>
+        <v>518669</v>
       </c>
       <c r="R18" t="n">
-        <v>7034392</v>
+        <v>7034375</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,7 +2457,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120467466</v>
+        <v>120467620</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2505,21 +2500,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518836</v>
+        <v>518727</v>
       </c>
       <c r="R19" t="n">
-        <v>7034593</v>
+        <v>7034329</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2565,11 +2560,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2596,7 +2586,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120467495</v>
+        <v>120467463</v>
       </c>
       <c r="B20" t="n">
         <v>57320</v>
@@ -2636,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518708</v>
+        <v>518865</v>
       </c>
       <c r="R20" t="n">
-        <v>7034368</v>
+        <v>7034523</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2676,7 +2666,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2703,7 +2693,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120467502</v>
+        <v>120467515</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2743,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518668</v>
+        <v>518690</v>
       </c>
       <c r="R21" t="n">
-        <v>7034378</v>
+        <v>7034072</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2810,7 +2800,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120467457</v>
+        <v>120467491</v>
       </c>
       <c r="B22" t="n">
         <v>57320</v>
@@ -2850,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518595</v>
+        <v>518772</v>
       </c>
       <c r="R22" t="n">
-        <v>7034382</v>
+        <v>7034366</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2880,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre 2 granar</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2917,7 +2907,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120467485</v>
+        <v>120467507</v>
       </c>
       <c r="B23" t="n">
         <v>57320</v>
@@ -2957,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518905</v>
+        <v>518607</v>
       </c>
       <c r="R23" t="n">
-        <v>7034396</v>
+        <v>7034347</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3024,7 +3014,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120467505</v>
+        <v>120467464</v>
       </c>
       <c r="B24" t="n">
         <v>57320</v>
@@ -3064,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518654</v>
+        <v>518883</v>
       </c>
       <c r="R24" t="n">
-        <v>7034382</v>
+        <v>7034525</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3104,7 +3094,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3131,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120467606</v>
+        <v>120467487</v>
       </c>
       <c r="B25" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3147,16 +3137,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3174,7 +3164,7 @@
         <v>518821</v>
       </c>
       <c r="R25" t="n">
-        <v>7034294</v>
+        <v>7034432</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3211,7 +3201,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3238,7 +3228,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120467494</v>
+        <v>120467467</v>
       </c>
       <c r="B26" t="n">
         <v>57320</v>
@@ -3278,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518723</v>
+        <v>518818</v>
       </c>
       <c r="R26" t="n">
-        <v>7034370</v>
+        <v>7034622</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3345,7 +3335,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120467490</v>
+        <v>120467482</v>
       </c>
       <c r="B27" t="n">
         <v>57320</v>
@@ -3385,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518794</v>
+        <v>518881</v>
       </c>
       <c r="R27" t="n">
-        <v>7034387</v>
+        <v>7034419</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3452,7 +3442,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120467497</v>
+        <v>120467457</v>
       </c>
       <c r="B28" t="n">
         <v>57320</v>
@@ -3492,10 +3482,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518674</v>
+        <v>518595</v>
       </c>
       <c r="R28" t="n">
-        <v>7034370</v>
+        <v>7034382</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3532,7 +3522,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre 2 granar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3559,7 +3549,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120467460</v>
+        <v>120467456</v>
       </c>
       <c r="B29" t="n">
         <v>57320</v>
@@ -3599,10 +3589,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518817</v>
+        <v>518584</v>
       </c>
       <c r="R29" t="n">
-        <v>7034450</v>
+        <v>7034352</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3639,7 +3629,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3666,10 +3656,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120467618</v>
+        <v>120467509</v>
       </c>
       <c r="B30" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3682,21 +3672,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3706,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518820</v>
+        <v>518608</v>
       </c>
       <c r="R30" t="n">
-        <v>7034294</v>
+        <v>7034284</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3742,6 +3732,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3768,7 +3763,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120467513</v>
+        <v>120467466</v>
       </c>
       <c r="B31" t="n">
         <v>57320</v>
@@ -3808,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>518705</v>
+        <v>518836</v>
       </c>
       <c r="R31" t="n">
-        <v>7034105</v>
+        <v>7034593</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3875,7 +3870,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120467478</v>
+        <v>120467517</v>
       </c>
       <c r="B32" t="n">
         <v>57320</v>
@@ -3915,10 +3910,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518932</v>
+        <v>518677</v>
       </c>
       <c r="R32" t="n">
-        <v>7034518</v>
+        <v>7034070</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3955,7 +3950,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3982,7 +3977,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120467467</v>
+        <v>120467510</v>
       </c>
       <c r="B33" t="n">
         <v>57320</v>
@@ -4022,10 +4017,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518818</v>
+        <v>518659</v>
       </c>
       <c r="R33" t="n">
-        <v>7034622</v>
+        <v>7034117</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4089,7 +4084,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120467453</v>
+        <v>120467454</v>
       </c>
       <c r="B34" t="n">
         <v>57320</v>
@@ -4129,10 +4124,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518578</v>
+        <v>518574</v>
       </c>
       <c r="R34" t="n">
-        <v>7034314</v>
+        <v>7034340</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4196,7 +4191,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120467496</v>
+        <v>120467475</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4236,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518682</v>
+        <v>519003</v>
       </c>
       <c r="R35" t="n">
-        <v>7034366</v>
+        <v>7034509</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4276,7 +4271,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4303,7 +4298,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120467454</v>
+        <v>120467451</v>
       </c>
       <c r="B36" t="n">
         <v>57320</v>
@@ -4343,10 +4338,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518574</v>
+        <v>518599</v>
       </c>
       <c r="R36" t="n">
-        <v>7034340</v>
+        <v>7034304</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4410,10 +4405,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120467469</v>
+        <v>120467617</v>
       </c>
       <c r="B37" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4426,21 +4421,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4450,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518862</v>
+        <v>518787</v>
       </c>
       <c r="R37" t="n">
-        <v>7034625</v>
+        <v>7034394</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4486,11 +4481,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4517,7 +4507,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120467462</v>
+        <v>120467492</v>
       </c>
       <c r="B38" t="n">
         <v>57320</v>
@@ -4557,10 +4547,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>518816</v>
+        <v>518765</v>
       </c>
       <c r="R38" t="n">
-        <v>7034466</v>
+        <v>7034291</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4624,7 +4614,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120467459</v>
+        <v>120467519</v>
       </c>
       <c r="B39" t="n">
         <v>57320</v>
@@ -4664,10 +4654,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>518766</v>
+        <v>518664</v>
       </c>
       <c r="R39" t="n">
-        <v>7034415</v>
+        <v>7034102</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4731,7 +4721,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120467518</v>
+        <v>120467495</v>
       </c>
       <c r="B40" t="n">
         <v>57320</v>
@@ -4771,10 +4761,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>518675</v>
+        <v>518708</v>
       </c>
       <c r="R40" t="n">
-        <v>7034072</v>
+        <v>7034368</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4811,7 +4801,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4838,7 +4828,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120467476</v>
+        <v>120467494</v>
       </c>
       <c r="B41" t="n">
         <v>57320</v>
@@ -4878,10 +4868,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518963</v>
+        <v>518723</v>
       </c>
       <c r="R41" t="n">
-        <v>7034492</v>
+        <v>7034370</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4918,7 +4908,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4945,7 +4935,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120467611</v>
+        <v>120467621</v>
       </c>
       <c r="B42" t="n">
         <v>90598</v>
@@ -4985,10 +4975,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518883</v>
+        <v>518701</v>
       </c>
       <c r="R42" t="n">
-        <v>7034541</v>
+        <v>7034127</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5047,10 +5037,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120467474</v>
+        <v>120467614</v>
       </c>
       <c r="B43" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5063,21 +5053,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5087,10 +5077,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519042</v>
+        <v>519001</v>
       </c>
       <c r="R43" t="n">
-        <v>7034514</v>
+        <v>7034557</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5123,11 +5113,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5154,7 +5139,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120467510</v>
+        <v>120467473</v>
       </c>
       <c r="B44" t="n">
         <v>57320</v>
@@ -5194,10 +5179,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518659</v>
+        <v>519024</v>
       </c>
       <c r="R44" t="n">
-        <v>7034117</v>
+        <v>7034532</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5261,7 +5246,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120467512</v>
+        <v>120467469</v>
       </c>
       <c r="B45" t="n">
         <v>57320</v>
@@ -5301,10 +5286,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518685</v>
+        <v>518862</v>
       </c>
       <c r="R45" t="n">
-        <v>7034116</v>
+        <v>7034625</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5368,7 +5353,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120467501</v>
+        <v>120467483</v>
       </c>
       <c r="B46" t="n">
         <v>57320</v>
@@ -5408,10 +5393,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518669</v>
+        <v>518888</v>
       </c>
       <c r="R46" t="n">
-        <v>7034375</v>
+        <v>7034422</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5448,7 +5433,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5475,7 +5460,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120467491</v>
+        <v>120467474</v>
       </c>
       <c r="B47" t="n">
         <v>57320</v>
@@ -5515,10 +5500,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518772</v>
+        <v>519042</v>
       </c>
       <c r="R47" t="n">
-        <v>7034366</v>
+        <v>7034514</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5582,7 +5567,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120467464</v>
+        <v>120467488</v>
       </c>
       <c r="B48" t="n">
         <v>57320</v>
@@ -5622,10 +5607,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518883</v>
+        <v>518792</v>
       </c>
       <c r="R48" t="n">
-        <v>7034525</v>
+        <v>7034416</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5662,7 +5647,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5689,7 +5674,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120467493</v>
+        <v>120467502</v>
       </c>
       <c r="B49" t="n">
         <v>57320</v>
@@ -5729,10 +5714,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518712</v>
+        <v>518668</v>
       </c>
       <c r="R49" t="n">
-        <v>7034336</v>
+        <v>7034378</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5769,7 +5754,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5796,7 +5781,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120467482</v>
+        <v>120467450</v>
       </c>
       <c r="B50" t="n">
         <v>57320</v>
@@ -5836,10 +5821,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518881</v>
+        <v>518565</v>
       </c>
       <c r="R50" t="n">
-        <v>7034419</v>
+        <v>7034294</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5903,7 +5888,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120467458</v>
+        <v>120467490</v>
       </c>
       <c r="B51" t="n">
         <v>57320</v>
@@ -5943,10 +5928,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518758</v>
+        <v>518794</v>
       </c>
       <c r="R51" t="n">
-        <v>7034403</v>
+        <v>7034387</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6010,10 +5995,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120467615</v>
+        <v>120467470</v>
       </c>
       <c r="B52" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6026,21 +6011,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6050,10 +6035,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>518904</v>
+        <v>518931</v>
       </c>
       <c r="R52" t="n">
-        <v>7034422</v>
+        <v>7034579</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6086,6 +6071,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6112,7 +6102,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120467487</v>
+        <v>120467500</v>
       </c>
       <c r="B53" t="n">
         <v>57320</v>
@@ -6152,10 +6142,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518821</v>
+        <v>518669</v>
       </c>
       <c r="R53" t="n">
-        <v>7034432</v>
+        <v>7034370</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6192,7 +6182,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6219,10 +6209,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120467620</v>
+        <v>120467520</v>
       </c>
       <c r="B54" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6235,21 +6225,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6259,10 +6249,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>518727</v>
+        <v>518661</v>
       </c>
       <c r="R54" t="n">
-        <v>7034329</v>
+        <v>7034107</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6295,6 +6285,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6321,10 +6316,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120467614</v>
+        <v>120467512</v>
       </c>
       <c r="B55" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6337,21 +6332,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6361,10 +6356,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>519001</v>
+        <v>518685</v>
       </c>
       <c r="R55" t="n">
-        <v>7034557</v>
+        <v>7034116</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6397,6 +6392,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6423,7 +6423,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120467515</v>
+        <v>120467484</v>
       </c>
       <c r="B56" t="n">
         <v>57320</v>
@@ -6463,10 +6463,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>518690</v>
+        <v>518914</v>
       </c>
       <c r="R56" t="n">
-        <v>7034072</v>
+        <v>7034381</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6530,7 +6530,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120467509</v>
+        <v>120467505</v>
       </c>
       <c r="B57" t="n">
         <v>57320</v>
@@ -6570,10 +6570,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>518608</v>
+        <v>518654</v>
       </c>
       <c r="R57" t="n">
-        <v>7034284</v>
+        <v>7034382</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6637,10 +6637,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120467612</v>
+        <v>120467460</v>
       </c>
       <c r="B58" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6653,21 +6653,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6677,10 +6677,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>518848</v>
+        <v>518817</v>
       </c>
       <c r="R58" t="n">
-        <v>7034595</v>
+        <v>7034450</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6713,6 +6713,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6739,7 +6744,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120467468</v>
+        <v>120467476</v>
       </c>
       <c r="B59" t="n">
         <v>57320</v>
@@ -6779,10 +6784,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>518830</v>
+        <v>518963</v>
       </c>
       <c r="R59" t="n">
-        <v>7034634</v>
+        <v>7034492</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6819,7 +6824,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6846,7 +6851,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120467456</v>
+        <v>120467472</v>
       </c>
       <c r="B60" t="n">
         <v>57320</v>
@@ -6886,10 +6891,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>518584</v>
+        <v>518975</v>
       </c>
       <c r="R60" t="n">
-        <v>7034352</v>
+        <v>7034569</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6953,7 +6958,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120467519</v>
+        <v>120467480</v>
       </c>
       <c r="B61" t="n">
         <v>57320</v>
@@ -6993,10 +6998,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>518664</v>
+        <v>518869</v>
       </c>
       <c r="R61" t="n">
-        <v>7034102</v>
+        <v>7034440</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7060,10 +7065,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120467480</v>
+        <v>120467611</v>
       </c>
       <c r="B62" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7076,21 +7081,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7100,10 +7105,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518869</v>
+        <v>518883</v>
       </c>
       <c r="R62" t="n">
-        <v>7034440</v>
+        <v>7034541</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7136,11 +7141,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7167,7 +7167,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120467511</v>
+        <v>120467518</v>
       </c>
       <c r="B63" t="n">
         <v>57320</v>
@@ -7207,10 +7207,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518672</v>
+        <v>518675</v>
       </c>
       <c r="R63" t="n">
-        <v>7034111</v>
+        <v>7034072</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7274,7 +7274,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120467506</v>
+        <v>120467462</v>
       </c>
       <c r="B64" t="n">
         <v>57320</v>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>518600</v>
+        <v>518816</v>
       </c>
       <c r="R64" t="n">
-        <v>7034354</v>
+        <v>7034466</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7381,10 +7381,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120467616</v>
+        <v>120467497</v>
       </c>
       <c r="B65" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7397,21 +7397,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7421,10 +7421,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518857</v>
+        <v>518674</v>
       </c>
       <c r="R65" t="n">
-        <v>7034399</v>
+        <v>7034370</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7457,6 +7457,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7483,10 +7488,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120467472</v>
+        <v>120467613</v>
       </c>
       <c r="B66" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7499,21 +7504,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7523,10 +7528,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518975</v>
+        <v>518801</v>
       </c>
       <c r="R66" t="n">
-        <v>7034569</v>
+        <v>7034574</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7559,11 +7564,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7590,10 +7590,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120467465</v>
+        <v>120467612</v>
       </c>
       <c r="B67" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7606,21 +7606,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7630,10 +7630,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>518877</v>
+        <v>518848</v>
       </c>
       <c r="R67" t="n">
-        <v>7034539</v>
+        <v>7034595</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7666,11 +7666,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Bohål ca 3,5-4 m upp i gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7697,7 +7692,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120467450</v>
+        <v>120467508</v>
       </c>
       <c r="B68" t="n">
         <v>57320</v>
@@ -7737,10 +7732,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518565</v>
+        <v>518608</v>
       </c>
       <c r="R68" t="n">
-        <v>7034294</v>
+        <v>7034344</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7804,7 +7799,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120467479</v>
+        <v>120467504</v>
       </c>
       <c r="B69" t="n">
         <v>57320</v>
@@ -7844,10 +7839,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>518926</v>
+        <v>518664</v>
       </c>
       <c r="R69" t="n">
-        <v>7034518</v>
+        <v>7034392</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7911,7 +7906,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120467517</v>
+        <v>120467452</v>
       </c>
       <c r="B70" t="n">
         <v>57320</v>
@@ -7951,10 +7946,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>518677</v>
+        <v>518591</v>
       </c>
       <c r="R70" t="n">
-        <v>7034070</v>
+        <v>7034299</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8018,10 +8013,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120467613</v>
+        <v>120467481</v>
       </c>
       <c r="B71" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8034,21 +8029,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8058,10 +8053,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>518801</v>
+        <v>518873</v>
       </c>
       <c r="R71" t="n">
-        <v>7034574</v>
+        <v>7034419</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8094,6 +8089,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8120,7 +8120,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120467484</v>
+        <v>120467493</v>
       </c>
       <c r="B72" t="n">
         <v>57320</v>
@@ -8160,10 +8160,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>518914</v>
+        <v>518712</v>
       </c>
       <c r="R72" t="n">
-        <v>7034381</v>
+        <v>7034336</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8200,7 +8200,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8227,7 +8227,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120467473</v>
+        <v>120467486</v>
       </c>
       <c r="B73" t="n">
         <v>57320</v>
@@ -8267,10 +8267,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>519024</v>
+        <v>518842</v>
       </c>
       <c r="R73" t="n">
-        <v>7034532</v>
+        <v>7034430</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8334,10 +8334,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120467621</v>
+        <v>120467458</v>
       </c>
       <c r="B74" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8350,21 +8350,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8374,10 +8374,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>518701</v>
+        <v>518758</v>
       </c>
       <c r="R74" t="n">
-        <v>7034127</v>
+        <v>7034403</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8410,6 +8410,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8436,7 +8441,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120467486</v>
+        <v>120467496</v>
       </c>
       <c r="B75" t="n">
         <v>57320</v>
@@ -8476,10 +8481,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>518842</v>
+        <v>518682</v>
       </c>
       <c r="R75" t="n">
-        <v>7034430</v>
+        <v>7034366</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8516,7 +8521,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8543,7 +8548,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120467508</v>
+        <v>120467471</v>
       </c>
       <c r="B76" t="n">
         <v>57320</v>
@@ -8583,10 +8588,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>518608</v>
+        <v>518950</v>
       </c>
       <c r="R76" t="n">
-        <v>7034344</v>
+        <v>7034577</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8650,10 +8655,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120467507</v>
+        <v>120467618</v>
       </c>
       <c r="B77" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8666,21 +8671,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8690,10 +8695,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>518607</v>
+        <v>518820</v>
       </c>
       <c r="R77" t="n">
-        <v>7034347</v>
+        <v>7034294</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8726,11 +8731,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8757,10 +8757,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120467481</v>
+        <v>120467616</v>
       </c>
       <c r="B78" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8773,21 +8773,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8797,10 +8797,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>518873</v>
+        <v>518857</v>
       </c>
       <c r="R78" t="n">
-        <v>7034419</v>
+        <v>7034399</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8833,11 +8833,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8864,10 +8859,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120467619</v>
+        <v>120467468</v>
       </c>
       <c r="B79" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8880,21 +8875,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8904,10 +8899,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>518812</v>
+        <v>518830</v>
       </c>
       <c r="R79" t="n">
-        <v>7034301</v>
+        <v>7034634</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8940,6 +8935,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8966,7 +8966,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120467451</v>
+        <v>120467479</v>
       </c>
       <c r="B80" t="n">
         <v>57320</v>
@@ -9006,10 +9006,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>518599</v>
+        <v>518926</v>
       </c>
       <c r="R80" t="n">
-        <v>7034304</v>
+        <v>7034518</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 56187-2019 artfynd.xlsx
+++ b/artfynd/A 56187-2019 artfynd.xlsx
@@ -7488,7 +7488,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120467613</v>
+        <v>120467612</v>
       </c>
       <c r="B66" t="n">
         <v>90598</v>
@@ -7528,10 +7528,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518801</v>
+        <v>518848</v>
       </c>
       <c r="R66" t="n">
-        <v>7034574</v>
+        <v>7034595</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7590,10 +7590,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120467612</v>
+        <v>120467508</v>
       </c>
       <c r="B67" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7606,21 +7606,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7630,10 +7630,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>518848</v>
+        <v>518608</v>
       </c>
       <c r="R67" t="n">
-        <v>7034595</v>
+        <v>7034344</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7666,6 +7666,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7692,7 +7697,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120467508</v>
+        <v>120467504</v>
       </c>
       <c r="B68" t="n">
         <v>57320</v>
@@ -7732,10 +7737,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518608</v>
+        <v>518664</v>
       </c>
       <c r="R68" t="n">
-        <v>7034344</v>
+        <v>7034392</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7799,10 +7804,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120467504</v>
+        <v>120467613</v>
       </c>
       <c r="B69" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7815,21 +7820,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7839,10 +7844,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>518664</v>
+        <v>518801</v>
       </c>
       <c r="R69" t="n">
-        <v>7034392</v>
+        <v>7034574</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7875,11 +7880,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 56187-2019 artfynd.xlsx
+++ b/artfynd/A 56187-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120467478</v>
+        <v>120467486</v>
       </c>
       <c r="B2" t="n">
         <v>57320</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518932</v>
+        <v>518842</v>
       </c>
       <c r="R2" t="n">
-        <v>7034518</v>
+        <v>7034430</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120467453</v>
+        <v>120467456</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518578</v>
+        <v>518584</v>
       </c>
       <c r="R3" t="n">
-        <v>7034314</v>
+        <v>7034352</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120467506</v>
+        <v>120467512</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518600</v>
+        <v>518685</v>
       </c>
       <c r="R4" t="n">
-        <v>7034354</v>
+        <v>7034116</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120467485</v>
+        <v>120467454</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518905</v>
+        <v>518574</v>
       </c>
       <c r="R5" t="n">
-        <v>7034396</v>
+        <v>7034340</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120467455</v>
+        <v>120467611</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518581</v>
+        <v>518883</v>
       </c>
       <c r="R6" t="n">
-        <v>7034337</v>
+        <v>7034541</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120467513</v>
+        <v>120467518</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518705</v>
+        <v>518675</v>
       </c>
       <c r="R7" t="n">
-        <v>7034105</v>
+        <v>7034072</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120467459</v>
+        <v>120467484</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1357,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518766</v>
+        <v>518914</v>
       </c>
       <c r="R8" t="n">
-        <v>7034415</v>
+        <v>7034381</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120467514</v>
+        <v>120467614</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518706</v>
+        <v>519001</v>
       </c>
       <c r="R9" t="n">
-        <v>7034110</v>
+        <v>7034557</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,11 +1495,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120467619</v>
+        <v>120467478</v>
       </c>
       <c r="B10" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518812</v>
+        <v>518932</v>
       </c>
       <c r="R10" t="n">
-        <v>7034301</v>
+        <v>7034518</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,6 +1597,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1740,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120467516</v>
+        <v>120467621</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518672</v>
+        <v>518701</v>
       </c>
       <c r="R12" t="n">
-        <v>7034063</v>
+        <v>7034127</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,11 +1811,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120467465</v>
+        <v>120467615</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,21 +1853,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518877</v>
+        <v>518904</v>
       </c>
       <c r="R13" t="n">
-        <v>7034539</v>
+        <v>7034422</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,11 +1913,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Bohål ca 3,5-4 m upp i gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,7 +1939,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120467489</v>
+        <v>120467496</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -1994,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518800</v>
+        <v>518682</v>
       </c>
       <c r="R14" t="n">
-        <v>7034389</v>
+        <v>7034366</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +2019,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120467498</v>
+        <v>120467506</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2101,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518670</v>
+        <v>518600</v>
       </c>
       <c r="R15" t="n">
-        <v>7034369</v>
+        <v>7034354</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2126,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120467606</v>
+        <v>120467464</v>
       </c>
       <c r="B16" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2184,16 +2169,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2208,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518821</v>
+        <v>518883</v>
       </c>
       <c r="R16" t="n">
-        <v>7034294</v>
+        <v>7034525</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2233,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120467615</v>
+        <v>120467455</v>
       </c>
       <c r="B17" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,21 +2276,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518904</v>
+        <v>518581</v>
       </c>
       <c r="R17" t="n">
-        <v>7034422</v>
+        <v>7034337</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2351,6 +2336,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,7 +2367,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120467501</v>
+        <v>120467497</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2417,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518669</v>
+        <v>518674</v>
       </c>
       <c r="R18" t="n">
-        <v>7034375</v>
+        <v>7034370</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2484,10 +2474,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120467620</v>
+        <v>120467517</v>
       </c>
       <c r="B19" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2500,21 +2490,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2524,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518727</v>
+        <v>518677</v>
       </c>
       <c r="R19" t="n">
-        <v>7034329</v>
+        <v>7034070</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,6 +2550,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2586,7 +2581,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120467463</v>
+        <v>120467474</v>
       </c>
       <c r="B20" t="n">
         <v>57320</v>
@@ -2626,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518865</v>
+        <v>519042</v>
       </c>
       <c r="R20" t="n">
-        <v>7034523</v>
+        <v>7034514</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2666,7 +2661,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2693,7 +2688,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120467515</v>
+        <v>120467467</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2733,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518690</v>
+        <v>518818</v>
       </c>
       <c r="R21" t="n">
-        <v>7034072</v>
+        <v>7034622</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2800,7 +2795,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120467491</v>
+        <v>120467510</v>
       </c>
       <c r="B22" t="n">
         <v>57320</v>
@@ -2840,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518772</v>
+        <v>518659</v>
       </c>
       <c r="R22" t="n">
-        <v>7034366</v>
+        <v>7034117</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,7 +2902,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120467507</v>
+        <v>120467470</v>
       </c>
       <c r="B23" t="n">
         <v>57320</v>
@@ -2947,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518607</v>
+        <v>518931</v>
       </c>
       <c r="R23" t="n">
-        <v>7034347</v>
+        <v>7034579</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2987,7 +2982,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,7 +3009,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120467464</v>
+        <v>120467460</v>
       </c>
       <c r="B24" t="n">
         <v>57320</v>
@@ -3054,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518883</v>
+        <v>518817</v>
       </c>
       <c r="R24" t="n">
-        <v>7034525</v>
+        <v>7034450</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3121,7 +3116,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120467487</v>
+        <v>120467493</v>
       </c>
       <c r="B25" t="n">
         <v>57320</v>
@@ -3161,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518821</v>
+        <v>518712</v>
       </c>
       <c r="R25" t="n">
-        <v>7034432</v>
+        <v>7034336</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3201,7 +3196,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,10 +3223,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120467467</v>
+        <v>120467620</v>
       </c>
       <c r="B26" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3244,21 +3239,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3268,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518818</v>
+        <v>518727</v>
       </c>
       <c r="R26" t="n">
-        <v>7034622</v>
+        <v>7034329</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3304,11 +3299,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3335,7 +3325,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120467482</v>
+        <v>120467505</v>
       </c>
       <c r="B27" t="n">
         <v>57320</v>
@@ -3375,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518881</v>
+        <v>518654</v>
       </c>
       <c r="R27" t="n">
-        <v>7034419</v>
+        <v>7034382</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3442,7 +3432,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120467457</v>
+        <v>120467492</v>
       </c>
       <c r="B28" t="n">
         <v>57320</v>
@@ -3482,10 +3472,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518595</v>
+        <v>518765</v>
       </c>
       <c r="R28" t="n">
-        <v>7034382</v>
+        <v>7034291</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3522,7 +3512,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre 2 granar</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3549,7 +3539,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120467456</v>
+        <v>120467451</v>
       </c>
       <c r="B29" t="n">
         <v>57320</v>
@@ -3589,10 +3579,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518584</v>
+        <v>518599</v>
       </c>
       <c r="R29" t="n">
-        <v>7034352</v>
+        <v>7034304</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3656,7 +3646,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120467509</v>
+        <v>120467459</v>
       </c>
       <c r="B30" t="n">
         <v>57320</v>
@@ -3696,10 +3686,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518608</v>
+        <v>518766</v>
       </c>
       <c r="R30" t="n">
-        <v>7034284</v>
+        <v>7034415</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3763,7 +3753,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120467466</v>
+        <v>120467494</v>
       </c>
       <c r="B31" t="n">
         <v>57320</v>
@@ -3803,10 +3793,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>518836</v>
+        <v>518723</v>
       </c>
       <c r="R31" t="n">
-        <v>7034593</v>
+        <v>7034370</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3870,7 +3860,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120467517</v>
+        <v>120467458</v>
       </c>
       <c r="B32" t="n">
         <v>57320</v>
@@ -3910,10 +3900,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518677</v>
+        <v>518758</v>
       </c>
       <c r="R32" t="n">
-        <v>7034070</v>
+        <v>7034403</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3977,7 +3967,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120467510</v>
+        <v>120467502</v>
       </c>
       <c r="B33" t="n">
         <v>57320</v>
@@ -4017,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518659</v>
+        <v>518668</v>
       </c>
       <c r="R33" t="n">
-        <v>7034117</v>
+        <v>7034378</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4084,7 +4074,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120467454</v>
+        <v>120467504</v>
       </c>
       <c r="B34" t="n">
         <v>57320</v>
@@ -4124,10 +4114,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518574</v>
+        <v>518664</v>
       </c>
       <c r="R34" t="n">
-        <v>7034340</v>
+        <v>7034392</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4191,7 +4181,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120467475</v>
+        <v>120467495</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4231,10 +4221,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>519003</v>
+        <v>518708</v>
       </c>
       <c r="R35" t="n">
-        <v>7034509</v>
+        <v>7034368</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4298,10 +4288,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120467451</v>
+        <v>120467613</v>
       </c>
       <c r="B36" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4314,21 +4304,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4338,10 +4328,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518599</v>
+        <v>518801</v>
       </c>
       <c r="R36" t="n">
-        <v>7034304</v>
+        <v>7034574</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4374,11 +4364,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4405,7 +4390,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120467617</v>
+        <v>120467619</v>
       </c>
       <c r="B37" t="n">
         <v>90598</v>
@@ -4445,10 +4430,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518787</v>
+        <v>518812</v>
       </c>
       <c r="R37" t="n">
-        <v>7034394</v>
+        <v>7034301</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4507,10 +4492,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120467492</v>
+        <v>120467612</v>
       </c>
       <c r="B38" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4523,21 +4508,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4547,10 +4532,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>518765</v>
+        <v>518848</v>
       </c>
       <c r="R38" t="n">
-        <v>7034291</v>
+        <v>7034595</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4583,11 +4568,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4614,10 +4594,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120467519</v>
+        <v>120467618</v>
       </c>
       <c r="B39" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4630,21 +4610,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4654,10 +4634,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>518664</v>
+        <v>518820</v>
       </c>
       <c r="R39" t="n">
-        <v>7034102</v>
+        <v>7034294</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4690,11 +4670,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4721,7 +4696,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120467495</v>
+        <v>120467500</v>
       </c>
       <c r="B40" t="n">
         <v>57320</v>
@@ -4761,10 +4736,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>518708</v>
+        <v>518669</v>
       </c>
       <c r="R40" t="n">
-        <v>7034368</v>
+        <v>7034370</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4801,7 +4776,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4828,7 +4803,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120467494</v>
+        <v>120467468</v>
       </c>
       <c r="B41" t="n">
         <v>57320</v>
@@ -4868,10 +4843,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518723</v>
+        <v>518830</v>
       </c>
       <c r="R41" t="n">
-        <v>7034370</v>
+        <v>7034634</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4935,10 +4910,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120467621</v>
+        <v>120467476</v>
       </c>
       <c r="B42" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4951,21 +4926,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4975,10 +4950,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518701</v>
+        <v>518963</v>
       </c>
       <c r="R42" t="n">
-        <v>7034127</v>
+        <v>7034492</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5011,6 +4986,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5037,10 +5017,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120467614</v>
+        <v>120467472</v>
       </c>
       <c r="B43" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5053,21 +5033,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5077,10 +5057,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519001</v>
+        <v>518975</v>
       </c>
       <c r="R43" t="n">
-        <v>7034557</v>
+        <v>7034569</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5113,6 +5093,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5139,7 +5124,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120467473</v>
+        <v>120467485</v>
       </c>
       <c r="B44" t="n">
         <v>57320</v>
@@ -5179,10 +5164,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519024</v>
+        <v>518905</v>
       </c>
       <c r="R44" t="n">
-        <v>7034532</v>
+        <v>7034396</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5219,7 +5204,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5246,7 +5231,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120467469</v>
+        <v>120467489</v>
       </c>
       <c r="B45" t="n">
         <v>57320</v>
@@ -5286,10 +5271,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518862</v>
+        <v>518800</v>
       </c>
       <c r="R45" t="n">
-        <v>7034625</v>
+        <v>7034389</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5353,7 +5338,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120467483</v>
+        <v>120467479</v>
       </c>
       <c r="B46" t="n">
         <v>57320</v>
@@ -5393,10 +5378,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518888</v>
+        <v>518926</v>
       </c>
       <c r="R46" t="n">
-        <v>7034422</v>
+        <v>7034518</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5460,7 +5445,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120467474</v>
+        <v>120467469</v>
       </c>
       <c r="B47" t="n">
         <v>57320</v>
@@ -5500,10 +5485,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519042</v>
+        <v>518862</v>
       </c>
       <c r="R47" t="n">
-        <v>7034514</v>
+        <v>7034625</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5567,7 +5552,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120467488</v>
+        <v>120467482</v>
       </c>
       <c r="B48" t="n">
         <v>57320</v>
@@ -5607,10 +5592,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518792</v>
+        <v>518881</v>
       </c>
       <c r="R48" t="n">
-        <v>7034416</v>
+        <v>7034419</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5674,7 +5659,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120467502</v>
+        <v>120467501</v>
       </c>
       <c r="B49" t="n">
         <v>57320</v>
@@ -5714,10 +5699,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518668</v>
+        <v>518669</v>
       </c>
       <c r="R49" t="n">
-        <v>7034378</v>
+        <v>7034375</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5754,7 +5739,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5781,7 +5766,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120467450</v>
+        <v>120467508</v>
       </c>
       <c r="B50" t="n">
         <v>57320</v>
@@ -5821,10 +5806,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518565</v>
+        <v>518608</v>
       </c>
       <c r="R50" t="n">
-        <v>7034294</v>
+        <v>7034344</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5888,7 +5873,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120467490</v>
+        <v>120467481</v>
       </c>
       <c r="B51" t="n">
         <v>57320</v>
@@ -5928,10 +5913,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518794</v>
+        <v>518873</v>
       </c>
       <c r="R51" t="n">
-        <v>7034387</v>
+        <v>7034419</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5995,7 +5980,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120467470</v>
+        <v>120467480</v>
       </c>
       <c r="B52" t="n">
         <v>57320</v>
@@ -6035,10 +6020,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>518931</v>
+        <v>518869</v>
       </c>
       <c r="R52" t="n">
-        <v>7034579</v>
+        <v>7034440</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6102,7 +6087,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120467500</v>
+        <v>120467514</v>
       </c>
       <c r="B53" t="n">
         <v>57320</v>
@@ -6142,10 +6127,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518669</v>
+        <v>518706</v>
       </c>
       <c r="R53" t="n">
-        <v>7034370</v>
+        <v>7034110</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6182,7 +6167,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6209,7 +6194,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120467520</v>
+        <v>120467490</v>
       </c>
       <c r="B54" t="n">
         <v>57320</v>
@@ -6249,10 +6234,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>518661</v>
+        <v>518794</v>
       </c>
       <c r="R54" t="n">
-        <v>7034107</v>
+        <v>7034387</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6316,7 +6301,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120467512</v>
+        <v>120467520</v>
       </c>
       <c r="B55" t="n">
         <v>57320</v>
@@ -6356,10 +6341,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>518685</v>
+        <v>518661</v>
       </c>
       <c r="R55" t="n">
-        <v>7034116</v>
+        <v>7034107</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6423,7 +6408,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120467484</v>
+        <v>120467457</v>
       </c>
       <c r="B56" t="n">
         <v>57320</v>
@@ -6463,10 +6448,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>518914</v>
+        <v>518595</v>
       </c>
       <c r="R56" t="n">
-        <v>7034381</v>
+        <v>7034382</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6503,7 +6488,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack äldre 2 granar</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6530,7 +6515,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120467505</v>
+        <v>120467491</v>
       </c>
       <c r="B57" t="n">
         <v>57320</v>
@@ -6570,10 +6555,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>518654</v>
+        <v>518772</v>
       </c>
       <c r="R57" t="n">
-        <v>7034382</v>
+        <v>7034366</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6637,7 +6622,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120467460</v>
+        <v>120467465</v>
       </c>
       <c r="B58" t="n">
         <v>57320</v>
@@ -6677,10 +6662,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>518817</v>
+        <v>518877</v>
       </c>
       <c r="R58" t="n">
-        <v>7034450</v>
+        <v>7034539</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6717,7 +6702,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Bohål ca 3,5-4 m upp i gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6744,10 +6729,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120467476</v>
+        <v>120467606</v>
       </c>
       <c r="B59" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6760,16 +6745,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6784,10 +6769,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>518963</v>
+        <v>518821</v>
       </c>
       <c r="R59" t="n">
-        <v>7034492</v>
+        <v>7034294</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6824,7 +6809,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6851,7 +6836,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120467472</v>
+        <v>120467450</v>
       </c>
       <c r="B60" t="n">
         <v>57320</v>
@@ -6891,10 +6876,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>518975</v>
+        <v>518565</v>
       </c>
       <c r="R60" t="n">
-        <v>7034569</v>
+        <v>7034294</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6958,7 +6943,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120467480</v>
+        <v>120467507</v>
       </c>
       <c r="B61" t="n">
         <v>57320</v>
@@ -6998,10 +6983,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>518869</v>
+        <v>518607</v>
       </c>
       <c r="R61" t="n">
-        <v>7034440</v>
+        <v>7034347</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7038,7 +7023,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7065,7 +7050,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120467611</v>
+        <v>120467616</v>
       </c>
       <c r="B62" t="n">
         <v>90598</v>
@@ -7105,10 +7090,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518883</v>
+        <v>518857</v>
       </c>
       <c r="R62" t="n">
-        <v>7034541</v>
+        <v>7034399</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7167,7 +7152,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120467518</v>
+        <v>120467483</v>
       </c>
       <c r="B63" t="n">
         <v>57320</v>
@@ -7207,10 +7192,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518675</v>
+        <v>518888</v>
       </c>
       <c r="R63" t="n">
-        <v>7034072</v>
+        <v>7034422</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7247,7 +7232,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7274,7 +7259,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120467462</v>
+        <v>120467453</v>
       </c>
       <c r="B64" t="n">
         <v>57320</v>
@@ -7314,10 +7299,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>518816</v>
+        <v>518578</v>
       </c>
       <c r="R64" t="n">
-        <v>7034466</v>
+        <v>7034314</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7354,7 +7339,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7381,7 +7366,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120467497</v>
+        <v>120467475</v>
       </c>
       <c r="B65" t="n">
         <v>57320</v>
@@ -7421,10 +7406,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518674</v>
+        <v>519003</v>
       </c>
       <c r="R65" t="n">
-        <v>7034370</v>
+        <v>7034509</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7461,7 +7446,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7488,10 +7473,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120467612</v>
+        <v>120467471</v>
       </c>
       <c r="B66" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7504,21 +7489,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7528,10 +7513,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518848</v>
+        <v>518950</v>
       </c>
       <c r="R66" t="n">
-        <v>7034595</v>
+        <v>7034577</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7564,6 +7549,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7590,7 +7580,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120467508</v>
+        <v>120467462</v>
       </c>
       <c r="B67" t="n">
         <v>57320</v>
@@ -7630,10 +7620,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>518608</v>
+        <v>518816</v>
       </c>
       <c r="R67" t="n">
-        <v>7034344</v>
+        <v>7034466</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7670,7 +7660,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7697,7 +7687,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120467504</v>
+        <v>120467487</v>
       </c>
       <c r="B68" t="n">
         <v>57320</v>
@@ -7737,10 +7727,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518664</v>
+        <v>518821</v>
       </c>
       <c r="R68" t="n">
-        <v>7034392</v>
+        <v>7034432</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7804,10 +7794,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120467613</v>
+        <v>120467463</v>
       </c>
       <c r="B69" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7820,21 +7810,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7844,10 +7834,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>518801</v>
+        <v>518865</v>
       </c>
       <c r="R69" t="n">
-        <v>7034574</v>
+        <v>7034523</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7880,6 +7870,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7906,7 +7901,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120467452</v>
+        <v>120467515</v>
       </c>
       <c r="B70" t="n">
         <v>57320</v>
@@ -7946,10 +7941,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>518591</v>
+        <v>518690</v>
       </c>
       <c r="R70" t="n">
-        <v>7034299</v>
+        <v>7034072</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8013,7 +8008,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120467481</v>
+        <v>120467452</v>
       </c>
       <c r="B71" t="n">
         <v>57320</v>
@@ -8053,10 +8048,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>518873</v>
+        <v>518591</v>
       </c>
       <c r="R71" t="n">
-        <v>7034419</v>
+        <v>7034299</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8120,10 +8115,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120467493</v>
+        <v>120467617</v>
       </c>
       <c r="B72" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8136,21 +8131,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8160,10 +8155,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>518712</v>
+        <v>518787</v>
       </c>
       <c r="R72" t="n">
-        <v>7034336</v>
+        <v>7034394</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8196,11 +8191,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8227,7 +8217,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120467486</v>
+        <v>120467509</v>
       </c>
       <c r="B73" t="n">
         <v>57320</v>
@@ -8267,10 +8257,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>518842</v>
+        <v>518608</v>
       </c>
       <c r="R73" t="n">
-        <v>7034430</v>
+        <v>7034284</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8334,7 +8324,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120467458</v>
+        <v>120467519</v>
       </c>
       <c r="B74" t="n">
         <v>57320</v>
@@ -8374,10 +8364,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>518758</v>
+        <v>518664</v>
       </c>
       <c r="R74" t="n">
-        <v>7034403</v>
+        <v>7034102</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8441,7 +8431,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120467496</v>
+        <v>120467513</v>
       </c>
       <c r="B75" t="n">
         <v>57320</v>
@@ -8481,10 +8471,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>518682</v>
+        <v>518705</v>
       </c>
       <c r="R75" t="n">
-        <v>7034366</v>
+        <v>7034105</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8521,7 +8511,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8548,7 +8538,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120467471</v>
+        <v>120467473</v>
       </c>
       <c r="B76" t="n">
         <v>57320</v>
@@ -8588,10 +8578,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>518950</v>
+        <v>519024</v>
       </c>
       <c r="R76" t="n">
-        <v>7034577</v>
+        <v>7034532</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8655,10 +8645,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120467618</v>
+        <v>120467466</v>
       </c>
       <c r="B77" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8671,21 +8661,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8695,10 +8685,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>518820</v>
+        <v>518836</v>
       </c>
       <c r="R77" t="n">
-        <v>7034294</v>
+        <v>7034593</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8731,6 +8721,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8757,10 +8752,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120467616</v>
+        <v>120467498</v>
       </c>
       <c r="B78" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8773,21 +8768,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8797,10 +8792,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>518857</v>
+        <v>518670</v>
       </c>
       <c r="R78" t="n">
-        <v>7034399</v>
+        <v>7034369</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8833,6 +8828,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8859,7 +8859,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120467468</v>
+        <v>120467488</v>
       </c>
       <c r="B79" t="n">
         <v>57320</v>
@@ -8899,10 +8899,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>518830</v>
+        <v>518792</v>
       </c>
       <c r="R79" t="n">
-        <v>7034634</v>
+        <v>7034416</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8966,7 +8966,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120467479</v>
+        <v>120467516</v>
       </c>
       <c r="B80" t="n">
         <v>57320</v>
@@ -9006,10 +9006,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>518926</v>
+        <v>518672</v>
       </c>
       <c r="R80" t="n">
-        <v>7034518</v>
+        <v>7034063</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">

--- a/artfynd/A 56187-2019 artfynd.xlsx
+++ b/artfynd/A 56187-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120467486</v>
+        <v>120467618</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518842</v>
+        <v>518820</v>
       </c>
       <c r="R2" t="n">
-        <v>7034430</v>
+        <v>7034294</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120467456</v>
+        <v>120467476</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518584</v>
+        <v>518963</v>
       </c>
       <c r="R3" t="n">
-        <v>7034352</v>
+        <v>7034492</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120467512</v>
+        <v>120467506</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518685</v>
+        <v>518600</v>
       </c>
       <c r="R4" t="n">
-        <v>7034116</v>
+        <v>7034354</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120467454</v>
+        <v>120467481</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518574</v>
+        <v>518873</v>
       </c>
       <c r="R5" t="n">
-        <v>7034340</v>
+        <v>7034419</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120467611</v>
+        <v>120467465</v>
       </c>
       <c r="B6" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518883</v>
+        <v>518877</v>
       </c>
       <c r="R6" t="n">
-        <v>7034541</v>
+        <v>7034539</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Bohål ca 3,5-4 m upp i gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120467518</v>
+        <v>120467466</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518675</v>
+        <v>518836</v>
       </c>
       <c r="R7" t="n">
-        <v>7034072</v>
+        <v>7034593</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120467484</v>
+        <v>120467479</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518914</v>
+        <v>518926</v>
       </c>
       <c r="R8" t="n">
-        <v>7034381</v>
+        <v>7034518</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120467614</v>
+        <v>120467617</v>
       </c>
       <c r="B9" t="n">
         <v>90598</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519001</v>
+        <v>518787</v>
       </c>
       <c r="R9" t="n">
-        <v>7034557</v>
+        <v>7034394</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120467478</v>
+        <v>120467619</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518932</v>
+        <v>518812</v>
       </c>
       <c r="R10" t="n">
-        <v>7034518</v>
+        <v>7034301</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,11 +1597,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Bohål</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,7 +1623,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120467511</v>
+        <v>120467458</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1668,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518672</v>
+        <v>518758</v>
       </c>
       <c r="R11" t="n">
-        <v>7034111</v>
+        <v>7034403</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120467621</v>
+        <v>120467475</v>
       </c>
       <c r="B12" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518701</v>
+        <v>519003</v>
       </c>
       <c r="R12" t="n">
-        <v>7034127</v>
+        <v>7034509</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,6 +1806,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,7 +1837,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120467615</v>
+        <v>120467616</v>
       </c>
       <c r="B13" t="n">
         <v>90598</v>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518904</v>
+        <v>518857</v>
       </c>
       <c r="R13" t="n">
-        <v>7034422</v>
+        <v>7034399</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1939,7 +1939,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120467496</v>
+        <v>120467520</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518682</v>
+        <v>518661</v>
       </c>
       <c r="R14" t="n">
-        <v>7034366</v>
+        <v>7034107</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120467506</v>
+        <v>120467495</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518600</v>
+        <v>518708</v>
       </c>
       <c r="R15" t="n">
-        <v>7034354</v>
+        <v>7034368</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,7 +2153,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120467464</v>
+        <v>120467514</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518883</v>
+        <v>518706</v>
       </c>
       <c r="R16" t="n">
-        <v>7034525</v>
+        <v>7034110</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,7 +2260,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120467455</v>
+        <v>120467490</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518581</v>
+        <v>518794</v>
       </c>
       <c r="R17" t="n">
-        <v>7034337</v>
+        <v>7034387</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,7 +2367,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120467497</v>
+        <v>120467505</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518674</v>
+        <v>518654</v>
       </c>
       <c r="R18" t="n">
-        <v>7034370</v>
+        <v>7034382</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,7 +2474,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120467517</v>
+        <v>120467469</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2514,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518677</v>
+        <v>518862</v>
       </c>
       <c r="R19" t="n">
-        <v>7034070</v>
+        <v>7034625</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2581,7 +2581,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120467474</v>
+        <v>120467457</v>
       </c>
       <c r="B20" t="n">
         <v>57320</v>
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519042</v>
+        <v>518595</v>
       </c>
       <c r="R20" t="n">
-        <v>7034514</v>
+        <v>7034382</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack äldre 2 granar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2688,7 +2688,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120467467</v>
+        <v>120467455</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518818</v>
+        <v>518581</v>
       </c>
       <c r="R21" t="n">
-        <v>7034622</v>
+        <v>7034337</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,7 +2795,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120467510</v>
+        <v>120467471</v>
       </c>
       <c r="B22" t="n">
         <v>57320</v>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518659</v>
+        <v>518950</v>
       </c>
       <c r="R22" t="n">
-        <v>7034117</v>
+        <v>7034577</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2902,10 +2902,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120467470</v>
+        <v>120467606</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2918,16 +2918,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518931</v>
+        <v>518821</v>
       </c>
       <c r="R23" t="n">
-        <v>7034579</v>
+        <v>7034294</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3009,7 +3009,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120467460</v>
+        <v>120467488</v>
       </c>
       <c r="B24" t="n">
         <v>57320</v>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518817</v>
+        <v>518792</v>
       </c>
       <c r="R24" t="n">
-        <v>7034450</v>
+        <v>7034416</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3116,7 +3116,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120467493</v>
+        <v>120467472</v>
       </c>
       <c r="B25" t="n">
         <v>57320</v>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518712</v>
+        <v>518975</v>
       </c>
       <c r="R25" t="n">
-        <v>7034336</v>
+        <v>7034569</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3223,10 +3223,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120467620</v>
+        <v>120467452</v>
       </c>
       <c r="B26" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3239,21 +3239,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3263,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518727</v>
+        <v>518591</v>
       </c>
       <c r="R26" t="n">
-        <v>7034329</v>
+        <v>7034299</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3299,6 +3299,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3325,7 +3330,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120467505</v>
+        <v>120467501</v>
       </c>
       <c r="B27" t="n">
         <v>57320</v>
@@ -3365,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518654</v>
+        <v>518669</v>
       </c>
       <c r="R27" t="n">
-        <v>7034382</v>
+        <v>7034375</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3405,7 +3410,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3432,7 +3437,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120467492</v>
+        <v>120467503</v>
       </c>
       <c r="B28" t="n">
         <v>57320</v>
@@ -3472,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518765</v>
+        <v>518668</v>
       </c>
       <c r="R28" t="n">
-        <v>7034291</v>
+        <v>7034378</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3512,7 +3517,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3539,7 +3544,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120467451</v>
+        <v>120467518</v>
       </c>
       <c r="B29" t="n">
         <v>57320</v>
@@ -3579,10 +3584,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518599</v>
+        <v>518675</v>
       </c>
       <c r="R29" t="n">
-        <v>7034304</v>
+        <v>7034072</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3619,7 +3624,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3646,7 +3651,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120467459</v>
+        <v>120467500</v>
       </c>
       <c r="B30" t="n">
         <v>57320</v>
@@ -3686,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518766</v>
+        <v>518669</v>
       </c>
       <c r="R30" t="n">
-        <v>7034415</v>
+        <v>7034370</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3726,7 +3731,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3753,7 +3758,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120467494</v>
+        <v>120467491</v>
       </c>
       <c r="B31" t="n">
         <v>57320</v>
@@ -3793,10 +3798,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>518723</v>
+        <v>518772</v>
       </c>
       <c r="R31" t="n">
-        <v>7034370</v>
+        <v>7034366</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3860,7 +3865,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120467458</v>
+        <v>120467474</v>
       </c>
       <c r="B32" t="n">
         <v>57320</v>
@@ -3900,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518758</v>
+        <v>519042</v>
       </c>
       <c r="R32" t="n">
-        <v>7034403</v>
+        <v>7034514</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3967,7 +3972,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120467502</v>
+        <v>120467470</v>
       </c>
       <c r="B33" t="n">
         <v>57320</v>
@@ -4007,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518668</v>
+        <v>518931</v>
       </c>
       <c r="R33" t="n">
-        <v>7034378</v>
+        <v>7034579</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4074,10 +4079,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120467504</v>
+        <v>120467613</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4090,21 +4095,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4114,10 +4119,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518664</v>
+        <v>518801</v>
       </c>
       <c r="R34" t="n">
-        <v>7034392</v>
+        <v>7034574</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4150,11 +4155,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4181,7 +4181,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120467495</v>
+        <v>120467468</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4221,10 +4221,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518708</v>
+        <v>518830</v>
       </c>
       <c r="R35" t="n">
-        <v>7034368</v>
+        <v>7034634</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4288,10 +4288,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120467613</v>
+        <v>120467485</v>
       </c>
       <c r="B36" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4304,21 +4304,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518801</v>
+        <v>518905</v>
       </c>
       <c r="R36" t="n">
-        <v>7034574</v>
+        <v>7034396</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4364,6 +4364,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4390,10 +4395,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120467619</v>
+        <v>120467459</v>
       </c>
       <c r="B37" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4406,21 +4411,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4430,10 +4435,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518812</v>
+        <v>518766</v>
       </c>
       <c r="R37" t="n">
-        <v>7034301</v>
+        <v>7034415</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4466,6 +4471,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4492,10 +4502,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120467612</v>
+        <v>120467510</v>
       </c>
       <c r="B38" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4508,21 +4518,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4532,10 +4542,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>518848</v>
+        <v>518659</v>
       </c>
       <c r="R38" t="n">
-        <v>7034595</v>
+        <v>7034117</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4568,6 +4578,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4594,10 +4609,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120467618</v>
+        <v>120467508</v>
       </c>
       <c r="B39" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4610,21 +4625,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4634,10 +4649,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>518820</v>
+        <v>518608</v>
       </c>
       <c r="R39" t="n">
-        <v>7034294</v>
+        <v>7034344</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4670,6 +4685,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4696,7 +4716,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120467500</v>
+        <v>120467489</v>
       </c>
       <c r="B40" t="n">
         <v>57320</v>
@@ -4736,10 +4756,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>518669</v>
+        <v>518800</v>
       </c>
       <c r="R40" t="n">
-        <v>7034370</v>
+        <v>7034389</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4776,7 +4796,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4803,7 +4823,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120467468</v>
+        <v>120467467</v>
       </c>
       <c r="B41" t="n">
         <v>57320</v>
@@ -4843,10 +4863,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518830</v>
+        <v>518818</v>
       </c>
       <c r="R41" t="n">
-        <v>7034634</v>
+        <v>7034622</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4910,7 +4930,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120467476</v>
+        <v>120467453</v>
       </c>
       <c r="B42" t="n">
         <v>57320</v>
@@ -4950,10 +4970,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518963</v>
+        <v>518578</v>
       </c>
       <c r="R42" t="n">
-        <v>7034492</v>
+        <v>7034314</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4990,7 +5010,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5017,7 +5037,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120467472</v>
+        <v>120467511</v>
       </c>
       <c r="B43" t="n">
         <v>57320</v>
@@ -5057,10 +5077,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>518975</v>
+        <v>518672</v>
       </c>
       <c r="R43" t="n">
-        <v>7034569</v>
+        <v>7034111</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5124,7 +5144,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120467485</v>
+        <v>120467512</v>
       </c>
       <c r="B44" t="n">
         <v>57320</v>
@@ -5164,10 +5184,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518905</v>
+        <v>518685</v>
       </c>
       <c r="R44" t="n">
-        <v>7034396</v>
+        <v>7034116</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5204,7 +5224,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5231,7 +5251,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120467489</v>
+        <v>120467497</v>
       </c>
       <c r="B45" t="n">
         <v>57320</v>
@@ -5271,10 +5291,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518800</v>
+        <v>518674</v>
       </c>
       <c r="R45" t="n">
-        <v>7034389</v>
+        <v>7034370</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5311,7 +5331,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5338,7 +5358,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120467479</v>
+        <v>120467493</v>
       </c>
       <c r="B46" t="n">
         <v>57320</v>
@@ -5378,10 +5398,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518926</v>
+        <v>518712</v>
       </c>
       <c r="R46" t="n">
-        <v>7034518</v>
+        <v>7034336</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5418,7 +5438,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5445,10 +5465,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120467469</v>
+        <v>120467621</v>
       </c>
       <c r="B47" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5461,21 +5481,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5485,10 +5505,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518862</v>
+        <v>518701</v>
       </c>
       <c r="R47" t="n">
-        <v>7034625</v>
+        <v>7034127</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5521,11 +5541,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5552,7 +5567,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120467482</v>
+        <v>120467487</v>
       </c>
       <c r="B48" t="n">
         <v>57320</v>
@@ -5592,10 +5607,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518881</v>
+        <v>518821</v>
       </c>
       <c r="R48" t="n">
-        <v>7034419</v>
+        <v>7034432</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5659,7 +5674,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120467501</v>
+        <v>120467483</v>
       </c>
       <c r="B49" t="n">
         <v>57320</v>
@@ -5699,10 +5714,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518669</v>
+        <v>518888</v>
       </c>
       <c r="R49" t="n">
-        <v>7034375</v>
+        <v>7034422</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5739,7 +5754,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5766,7 +5781,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120467508</v>
+        <v>120467463</v>
       </c>
       <c r="B50" t="n">
         <v>57320</v>
@@ -5806,10 +5821,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518608</v>
+        <v>518865</v>
       </c>
       <c r="R50" t="n">
-        <v>7034344</v>
+        <v>7034523</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5846,7 +5861,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5873,7 +5888,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120467481</v>
+        <v>120467496</v>
       </c>
       <c r="B51" t="n">
         <v>57320</v>
@@ -5913,10 +5928,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518873</v>
+        <v>518682</v>
       </c>
       <c r="R51" t="n">
-        <v>7034419</v>
+        <v>7034366</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5953,7 +5968,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5980,7 +5995,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120467480</v>
+        <v>120467451</v>
       </c>
       <c r="B52" t="n">
         <v>57320</v>
@@ -6020,10 +6035,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>518869</v>
+        <v>518599</v>
       </c>
       <c r="R52" t="n">
-        <v>7034440</v>
+        <v>7034304</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6087,7 +6102,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120467514</v>
+        <v>120467517</v>
       </c>
       <c r="B53" t="n">
         <v>57320</v>
@@ -6127,10 +6142,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518706</v>
+        <v>518677</v>
       </c>
       <c r="R53" t="n">
-        <v>7034110</v>
+        <v>7034070</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6194,7 +6209,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120467490</v>
+        <v>120467460</v>
       </c>
       <c r="B54" t="n">
         <v>57320</v>
@@ -6234,10 +6249,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>518794</v>
+        <v>518817</v>
       </c>
       <c r="R54" t="n">
-        <v>7034387</v>
+        <v>7034450</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6274,7 +6289,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6301,7 +6316,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120467520</v>
+        <v>120467482</v>
       </c>
       <c r="B55" t="n">
         <v>57320</v>
@@ -6341,10 +6356,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>518661</v>
+        <v>518881</v>
       </c>
       <c r="R55" t="n">
-        <v>7034107</v>
+        <v>7034419</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6408,7 +6423,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120467457</v>
+        <v>120467462</v>
       </c>
       <c r="B56" t="n">
         <v>57320</v>
@@ -6448,10 +6463,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>518595</v>
+        <v>518816</v>
       </c>
       <c r="R56" t="n">
-        <v>7034382</v>
+        <v>7034466</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6488,7 +6503,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack äldre 2 granar</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6515,7 +6530,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120467491</v>
+        <v>120467480</v>
       </c>
       <c r="B57" t="n">
         <v>57320</v>
@@ -6555,10 +6570,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>518772</v>
+        <v>518869</v>
       </c>
       <c r="R57" t="n">
-        <v>7034366</v>
+        <v>7034440</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6622,7 +6637,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120467465</v>
+        <v>120467464</v>
       </c>
       <c r="B58" t="n">
         <v>57320</v>
@@ -6662,10 +6677,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>518877</v>
+        <v>518883</v>
       </c>
       <c r="R58" t="n">
-        <v>7034539</v>
+        <v>7034525</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6702,7 +6717,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Bohål ca 3,5-4 m upp i gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6729,10 +6744,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120467606</v>
+        <v>120467513</v>
       </c>
       <c r="B59" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6745,16 +6760,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6769,10 +6784,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>518821</v>
+        <v>518705</v>
       </c>
       <c r="R59" t="n">
-        <v>7034294</v>
+        <v>7034105</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6809,7 +6824,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6836,7 +6851,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120467450</v>
+        <v>120467498</v>
       </c>
       <c r="B60" t="n">
         <v>57320</v>
@@ -6876,10 +6891,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>518565</v>
+        <v>518670</v>
       </c>
       <c r="R60" t="n">
-        <v>7034294</v>
+        <v>7034369</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6916,7 +6931,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6943,10 +6958,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120467507</v>
+        <v>120467612</v>
       </c>
       <c r="B61" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6959,21 +6974,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6983,10 +6998,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>518607</v>
+        <v>518848</v>
       </c>
       <c r="R61" t="n">
-        <v>7034347</v>
+        <v>7034595</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7019,11 +7034,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7050,7 +7060,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120467616</v>
+        <v>120467611</v>
       </c>
       <c r="B62" t="n">
         <v>90598</v>
@@ -7090,10 +7100,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518857</v>
+        <v>518883</v>
       </c>
       <c r="R62" t="n">
-        <v>7034399</v>
+        <v>7034541</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7152,7 +7162,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120467483</v>
+        <v>120467516</v>
       </c>
       <c r="B63" t="n">
         <v>57320</v>
@@ -7192,10 +7202,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518888</v>
+        <v>518672</v>
       </c>
       <c r="R63" t="n">
-        <v>7034422</v>
+        <v>7034063</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7232,7 +7242,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7259,7 +7269,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120467453</v>
+        <v>120467478</v>
       </c>
       <c r="B64" t="n">
         <v>57320</v>
@@ -7299,10 +7309,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>518578</v>
+        <v>518932</v>
       </c>
       <c r="R64" t="n">
-        <v>7034314</v>
+        <v>7034518</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7339,7 +7349,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7366,7 +7376,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120467475</v>
+        <v>120467486</v>
       </c>
       <c r="B65" t="n">
         <v>57320</v>
@@ -7406,10 +7416,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>519003</v>
+        <v>518842</v>
       </c>
       <c r="R65" t="n">
-        <v>7034509</v>
+        <v>7034430</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7473,7 +7483,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120467471</v>
+        <v>120467492</v>
       </c>
       <c r="B66" t="n">
         <v>57320</v>
@@ -7513,10 +7523,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518950</v>
+        <v>518765</v>
       </c>
       <c r="R66" t="n">
-        <v>7034577</v>
+        <v>7034291</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7553,7 +7563,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7580,10 +7590,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120467462</v>
+        <v>120467620</v>
       </c>
       <c r="B67" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7596,21 +7606,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7620,10 +7630,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>518816</v>
+        <v>518727</v>
       </c>
       <c r="R67" t="n">
-        <v>7034466</v>
+        <v>7034329</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7656,11 +7666,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7687,7 +7692,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120467487</v>
+        <v>120467519</v>
       </c>
       <c r="B68" t="n">
         <v>57320</v>
@@ -7727,10 +7732,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518821</v>
+        <v>518664</v>
       </c>
       <c r="R68" t="n">
-        <v>7034432</v>
+        <v>7034102</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7794,7 +7799,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120467463</v>
+        <v>120467450</v>
       </c>
       <c r="B69" t="n">
         <v>57320</v>
@@ -7834,10 +7839,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>518865</v>
+        <v>518565</v>
       </c>
       <c r="R69" t="n">
-        <v>7034523</v>
+        <v>7034294</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7874,7 +7879,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7901,7 +7906,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120467515</v>
+        <v>120467504</v>
       </c>
       <c r="B70" t="n">
         <v>57320</v>
@@ -7941,10 +7946,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>518690</v>
+        <v>518664</v>
       </c>
       <c r="R70" t="n">
-        <v>7034072</v>
+        <v>7034392</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8008,7 +8013,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120467452</v>
+        <v>120467484</v>
       </c>
       <c r="B71" t="n">
         <v>57320</v>
@@ -8048,10 +8053,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>518591</v>
+        <v>518914</v>
       </c>
       <c r="R71" t="n">
-        <v>7034299</v>
+        <v>7034381</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8115,10 +8120,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120467617</v>
+        <v>120467454</v>
       </c>
       <c r="B72" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8131,21 +8136,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8155,10 +8160,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>518787</v>
+        <v>518574</v>
       </c>
       <c r="R72" t="n">
-        <v>7034394</v>
+        <v>7034340</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8191,6 +8196,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8217,7 +8227,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120467509</v>
+        <v>120467515</v>
       </c>
       <c r="B73" t="n">
         <v>57320</v>
@@ -8257,10 +8267,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>518608</v>
+        <v>518690</v>
       </c>
       <c r="R73" t="n">
-        <v>7034284</v>
+        <v>7034072</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8324,7 +8334,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120467519</v>
+        <v>120467509</v>
       </c>
       <c r="B74" t="n">
         <v>57320</v>
@@ -8364,10 +8374,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>518664</v>
+        <v>518608</v>
       </c>
       <c r="R74" t="n">
-        <v>7034102</v>
+        <v>7034284</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8431,10 +8441,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120467513</v>
+        <v>120467614</v>
       </c>
       <c r="B75" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8447,21 +8457,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8471,10 +8481,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>518705</v>
+        <v>519001</v>
       </c>
       <c r="R75" t="n">
-        <v>7034105</v>
+        <v>7034557</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8507,11 +8517,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8538,10 +8543,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120467473</v>
+        <v>120467615</v>
       </c>
       <c r="B76" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8554,21 +8559,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8578,10 +8583,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>519024</v>
+        <v>518904</v>
       </c>
       <c r="R76" t="n">
-        <v>7034532</v>
+        <v>7034422</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8614,11 +8619,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8645,7 +8645,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120467466</v>
+        <v>120467473</v>
       </c>
       <c r="B77" t="n">
         <v>57320</v>
@@ -8685,10 +8685,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>518836</v>
+        <v>519024</v>
       </c>
       <c r="R77" t="n">
-        <v>7034593</v>
+        <v>7034532</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8752,7 +8752,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120467498</v>
+        <v>120467456</v>
       </c>
       <c r="B78" t="n">
         <v>57320</v>
@@ -8792,10 +8792,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>518670</v>
+        <v>518584</v>
       </c>
       <c r="R78" t="n">
-        <v>7034369</v>
+        <v>7034352</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8859,7 +8859,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120467488</v>
+        <v>120467494</v>
       </c>
       <c r="B79" t="n">
         <v>57320</v>
@@ -8899,10 +8899,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>518792</v>
+        <v>518723</v>
       </c>
       <c r="R79" t="n">
-        <v>7034416</v>
+        <v>7034370</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8966,7 +8966,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120467516</v>
+        <v>120467507</v>
       </c>
       <c r="B80" t="n">
         <v>57320</v>
@@ -9006,10 +9006,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>518672</v>
+        <v>518607</v>
       </c>
       <c r="R80" t="n">
-        <v>7034063</v>
+        <v>7034347</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">

--- a/artfynd/A 56187-2019 artfynd.xlsx
+++ b/artfynd/A 56187-2019 artfynd.xlsx
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120467466</v>
+        <v>120467617</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518836</v>
+        <v>518787</v>
       </c>
       <c r="R7" t="n">
-        <v>7034593</v>
+        <v>7034394</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120467479</v>
+        <v>120467619</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518926</v>
+        <v>518812</v>
       </c>
       <c r="R8" t="n">
-        <v>7034518</v>
+        <v>7034301</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,11 +1383,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120467617</v>
+        <v>120467466</v>
       </c>
       <c r="B9" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518787</v>
+        <v>518836</v>
       </c>
       <c r="R9" t="n">
-        <v>7034394</v>
+        <v>7034593</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,6 +1485,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120467619</v>
+        <v>120467479</v>
       </c>
       <c r="B10" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518812</v>
+        <v>518926</v>
       </c>
       <c r="R10" t="n">
-        <v>7034301</v>
+        <v>7034518</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,6 +1592,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -3651,10 +3651,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120467500</v>
+        <v>120467613</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3667,21 +3667,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518669</v>
+        <v>518801</v>
       </c>
       <c r="R30" t="n">
-        <v>7034370</v>
+        <v>7034574</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3727,11 +3727,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3758,7 +3753,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120467491</v>
+        <v>120467500</v>
       </c>
       <c r="B31" t="n">
         <v>57320</v>
@@ -3798,10 +3793,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>518772</v>
+        <v>518669</v>
       </c>
       <c r="R31" t="n">
-        <v>7034366</v>
+        <v>7034370</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,7 +3833,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3865,7 +3860,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120467474</v>
+        <v>120467491</v>
       </c>
       <c r="B32" t="n">
         <v>57320</v>
@@ -3905,10 +3900,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519042</v>
+        <v>518772</v>
       </c>
       <c r="R32" t="n">
-        <v>7034514</v>
+        <v>7034366</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3972,7 +3967,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120467470</v>
+        <v>120467474</v>
       </c>
       <c r="B33" t="n">
         <v>57320</v>
@@ -4012,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518931</v>
+        <v>519042</v>
       </c>
       <c r="R33" t="n">
-        <v>7034579</v>
+        <v>7034514</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4079,10 +4074,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120467613</v>
+        <v>120467470</v>
       </c>
       <c r="B34" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4095,21 +4090,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4119,10 +4114,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518801</v>
+        <v>518931</v>
       </c>
       <c r="R34" t="n">
-        <v>7034574</v>
+        <v>7034579</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4155,6 +4150,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
